--- a/jira_export_2026-08-21.xlsx
+++ b/jira_export_2026-08-21.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>342 h</t>
+          <t>349 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>264</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -3661,7 +3661,7 @@
         <v>2</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>8.75</v>
+        <v>9</v>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>416.29</v>
       </c>
       <c r="P41" s="12" t="n">
-        <v>47.58</v>
+        <v>46.25</v>
       </c>
     </row>
     <row r="42">
@@ -3949,7 +3949,7 @@
         <v>2</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>8232.900000000001</v>
       </c>
       <c r="P136" s="18" t="n">
-        <v>43.62</v>
+        <v>43.33</v>
       </c>
     </row>
   </sheetData>
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>139.25</v>
+        <v>139.5</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>27.25</v>
@@ -11041,7 +11041,7 @@
         <v>7.5</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>174</v>
+        <v>174.25</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>62.25</v>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>29.0%</t>
         </is>
       </c>
     </row>
@@ -11062,7 +11062,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
@@ -11071,17 +11071,17 @@
         <v>1.25</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>14.75</v>
+        <v>15.75</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>103.74</v>
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>15.2%</t>
         </is>
       </c>
     </row>
@@ -11093,7 +11093,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -11257,7 +11257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11281,7 +11281,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 12 commande(s)</t>
+          <t>Épics créées ce mois — 13 commande(s)</t>
         </is>
       </c>
     </row>
@@ -11651,22 +11651,22 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35041</t>
+          <t>PDMDEP-35188</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35037</t>
+          <t>PDMDEP-35184</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
+          <t>COMMUNE DE GAILLARD</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>00178778</t>
+          <t>00178947</t>
         </is>
       </c>
       <c r="I12" s="26" t="n">
@@ -11696,22 +11696,22 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34993</t>
+          <t>PDMDEP-35041</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34989</t>
+          <t>PDMDEP-35037</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>Commune de Villeneuve D'Ascq</t>
+          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -11731,32 +11731,32 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>00178306</t>
+          <t>00178778</t>
         </is>
       </c>
       <c r="I13" s="25" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34979</t>
+          <t>PDMDEP-34993</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34975</t>
+          <t>PDMDEP-34989</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>Commune de Villeneuve D'Ascq</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -11776,22 +11776,22 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>00178226</t>
+          <t>00178306</t>
         </is>
       </c>
       <c r="I14" s="26" t="n">
-        <v>2200</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34970</t>
+          <t>PDMDEP-34979</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34966</t>
+          <t>PDMDEP-34975</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Commune de Villeneuve D'Ascq</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -11821,83 +11821,107 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>00146508</t>
+          <t>00178226</t>
         </is>
       </c>
       <c r="I15" s="25" t="n">
-        <v>0</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-34970</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34966</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Commune de Villeneuve D'Ascq</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>00146508</t>
+        </is>
+      </c>
+      <c r="I16" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
           <t>PDMDEP-34929</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>PDMDEP-34925</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>04/08/2026</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t>00178034</t>
         </is>
       </c>
-      <c r="I16" s="26" t="n">
+      <c r="I17" s="25" t="n">
         <v>2300</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="n"/>
-      <c r="C17" s="17" t="n"/>
-      <c r="D17" s="17" t="n"/>
-      <c r="E17" s="17" t="n"/>
-      <c r="F17" s="17" t="n"/>
-      <c r="G17" s="17" t="n"/>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t>12 commande(s)</t>
-        </is>
-      </c>
-      <c r="I17" s="24" t="n">
-        <v>15076</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B18" s="17" t="n"/>
@@ -11908,17 +11932,17 @@
       <c r="G18" s="17" t="n"/>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t>5 commande(s)</t>
+          <t>13 commande(s)</t>
         </is>
       </c>
       <c r="I18" s="24" t="n">
-        <v>6000</v>
+        <v>15076</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B19" s="17" t="n"/>
@@ -11929,10 +11953,31 @@
       <c r="G19" s="17" t="n"/>
       <c r="H19" s="17" t="inlineStr">
         <is>
+          <t>6 commande(s)</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
+      <c r="G20" s="17" t="n"/>
+      <c r="H20" s="17" t="inlineStr">
+        <is>
           <t>7 commande(s)</t>
         </is>
       </c>
-      <c r="I19" s="24" t="n">
+      <c r="I20" s="24" t="n">
         <v>9076</v>
       </c>
     </row>

--- a/jira_export_2026-08-21.xlsx
+++ b/jira_export_2026-08-21.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>8,233 €</t>
+          <t>13,494 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,14 +760,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>3,633 €</t>
+          <t>5,360 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>4,600 €</t>
+          <t>8,134 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>349 h</t>
+          <t>358 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P136"/>
+  <dimension ref="A1:P137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -3316,11 +3316,11 @@
       <c r="N36" s="15" t="n">
         <v>242.9</v>
       </c>
-      <c r="O36" s="16" t="n">
-        <v>0</v>
+      <c r="O36" s="15" t="n">
+        <v>1118.61</v>
       </c>
       <c r="P36" s="15" t="n">
-        <v>0</v>
+        <v>114.73</v>
       </c>
     </row>
     <row r="37">
@@ -3965,10 +3965,10 @@
         <v>4040</v>
       </c>
       <c r="O45" s="16" t="n">
-        <v>0</v>
+        <v>3535</v>
       </c>
       <c r="P45" s="12" t="n">
-        <v>0</v>
+        <v>1571.11</v>
       </c>
     </row>
     <row r="46">
@@ -4541,10 +4541,10 @@
         <v>625</v>
       </c>
       <c r="O53" s="16" t="n">
-        <v>0</v>
+        <v>607.5</v>
       </c>
       <c r="P53" s="12" t="n">
-        <v>0</v>
+        <v>121.5</v>
       </c>
     </row>
     <row r="54">
@@ -4982,12 +4982,12 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
@@ -5022,44 +5022,44 @@
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J60" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K60" s="14" t="n">
-        <v>2.75</v>
+        <v>0.25</v>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>1294.224</v>
-      </c>
-      <c r="O60" s="16" t="n">
-        <v>219.36</v>
+        <v>0</v>
+      </c>
+      <c r="O60" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="P60" s="15" t="n">
-        <v>79.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32565</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Afficher les AP signé avant MEP WFS</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
@@ -5094,36 +5094,44 @@
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L61" s="11" t="inlineStr"/>
-      <c r="M61" s="11" t="inlineStr"/>
+        <v>2.75</v>
+      </c>
+      <c r="L61" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-32629</t>
+        </is>
+      </c>
+      <c r="M61" s="11" t="inlineStr">
+        <is>
+          <t>00163182</t>
+        </is>
+      </c>
       <c r="N61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="12" t="n">
-        <v>0</v>
+        <v>1294.224</v>
+      </c>
+      <c r="O61" s="16" t="n">
+        <v>219.36</v>
       </c>
       <c r="P61" s="12" t="n">
-        <v>0</v>
+        <v>79.77</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32565</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
@@ -5133,12 +5141,12 @@
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
@@ -5148,7 +5156,7 @@
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H62" s="14" t="inlineStr">
@@ -5165,22 +5173,14 @@
         <v>4</v>
       </c>
       <c r="K62" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-32556</t>
-        </is>
-      </c>
-      <c r="M62" s="14" t="inlineStr">
-        <is>
-          <t>00162313</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L62" s="14" t="inlineStr"/>
+      <c r="M62" s="14" t="inlineStr"/>
       <c r="N62" s="15" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O62" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P62" s="15" t="n">
@@ -5190,32 +5190,32 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
@@ -5225,32 +5225,32 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K63" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>2335</v>
+        <v>142.1</v>
       </c>
       <c r="O63" s="16" t="n">
         <v>0</v>
@@ -5262,32 +5262,32 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -5297,34 +5297,34 @@
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K64" s="14" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N64" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="15" t="n">
+        <v>2335</v>
+      </c>
+      <c r="O64" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P64" s="15" t="n">
@@ -5334,32 +5334,32 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
@@ -5369,34 +5369,34 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>450</v>
-      </c>
-      <c r="O65" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P65" s="12" t="n">
@@ -5406,32 +5406,32 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
@@ -5441,32 +5441,32 @@
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K66" s="14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O66" s="16" t="n">
         <v>0</v>
@@ -5478,28 +5478,32 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32152</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
-        </is>
-      </c>
-      <c r="C67" s="11" t="inlineStr"/>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
@@ -5509,32 +5513,32 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32161</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00160661</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>255</v>
+        <v>910</v>
       </c>
       <c r="O67" s="16" t="n">
         <v>0</v>
@@ -5546,27 +5550,23 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
-        </is>
-      </c>
-      <c r="C68" s="14" t="inlineStr">
-        <is>
-          <t>Alizée MARGOT</t>
-        </is>
-      </c>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="inlineStr"/>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
@@ -5593,52 +5593,52 @@
         <v>5</v>
       </c>
       <c r="K68" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="15" t="n">
-        <v>100</v>
+        <v>255</v>
+      </c>
+      <c r="O68" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P68" s="15" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
@@ -5653,49 +5653,49 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>590.15</v>
-      </c>
-      <c r="O69" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O69" s="12" t="n">
+        <v>100</v>
       </c>
       <c r="P69" s="12" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
@@ -5741,16 +5741,16 @@
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>1000</v>
+        <v>590.15</v>
       </c>
       <c r="O70" s="16" t="n">
         <v>0</v>
@@ -5762,32 +5762,32 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
@@ -5797,34 +5797,34 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>11.75</v>
+        <v>0</v>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" s="12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O71" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P71" s="12" t="n">
@@ -5834,32 +5834,32 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
@@ -5869,34 +5869,34 @@
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K72" s="14" t="n">
-        <v>0</v>
+        <v>11.75</v>
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
-        <v>285</v>
-      </c>
-      <c r="O72" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P72" s="15" t="n">
@@ -5906,32 +5906,32 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
@@ -5957,16 +5957,16 @@
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>1325</v>
+        <v>285</v>
       </c>
       <c r="O73" s="16" t="n">
         <v>0</v>
@@ -5978,12 +5978,12 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
@@ -5993,12 +5993,12 @@
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
@@ -6029,16 +6029,16 @@
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>120</v>
+        <v>1325</v>
       </c>
       <c r="O74" s="16" t="n">
         <v>0</v>
@@ -6050,32 +6050,32 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
@@ -6101,16 +6101,16 @@
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="O75" s="16" t="n">
         <v>0</v>
@@ -6122,27 +6122,27 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
@@ -6157,32 +6157,32 @@
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K76" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>203.5</v>
+        <v>588</v>
       </c>
       <c r="O76" s="16" t="n">
         <v>0</v>
@@ -6194,12 +6194,12 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
@@ -6209,12 +6209,12 @@
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -6229,12 +6229,12 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
@@ -6245,16 +6245,16 @@
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>300</v>
+        <v>203.5</v>
       </c>
       <c r="O77" s="16" t="n">
         <v>0</v>
@@ -6266,32 +6266,32 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
@@ -6301,32 +6301,32 @@
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K78" s="14" t="n">
-        <v>12.25</v>
+        <v>0</v>
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="O78" s="16" t="n">
         <v>0</v>
@@ -6338,12 +6338,12 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31528</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LILLE] - Màj carto</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
@@ -6353,12 +6353,12 @@
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="G79" s="11" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H79" s="11" t="inlineStr">
@@ -6385,14 +6385,22 @@
         <v>6</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L79" s="11" t="inlineStr"/>
-      <c r="M79" s="11" t="inlineStr"/>
+        <v>12.25</v>
+      </c>
+      <c r="L79" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-31546</t>
+        </is>
+      </c>
+      <c r="M79" s="11" t="inlineStr">
+        <is>
+          <t>00157816</t>
+        </is>
+      </c>
       <c r="N79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" s="12" t="n">
+        <v>700</v>
+      </c>
+      <c r="O79" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P79" s="12" t="n">
@@ -6402,27 +6410,27 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31528</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE LILLE] - Màj carto</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
@@ -6432,7 +6440,7 @@
       </c>
       <c r="G80" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H80" s="14" t="inlineStr">
@@ -6442,29 +6450,21 @@
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K80" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="L80" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-31468</t>
-        </is>
-      </c>
-      <c r="M80" s="14" t="inlineStr">
-        <is>
-          <t>00157346</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L80" s="14" t="inlineStr"/>
+      <c r="M80" s="14" t="inlineStr"/>
       <c r="N80" s="15" t="n">
-        <v>416.475</v>
-      </c>
-      <c r="O80" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="15" t="n">
@@ -6474,32 +6474,32 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
@@ -6509,32 +6509,32 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>210</v>
+        <v>416.475</v>
       </c>
       <c r="O81" s="16" t="n">
         <v>0</v>
@@ -6546,12 +6546,12 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F82" s="14" t="inlineStr">
@@ -6597,16 +6597,16 @@
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
-        <v>281</v>
+        <v>210</v>
       </c>
       <c r="O82" s="16" t="n">
         <v>0</v>
@@ -6618,12 +6618,12 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
@@ -6633,12 +6633,12 @@
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
@@ -6669,16 +6669,16 @@
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>130</v>
+        <v>281</v>
       </c>
       <c r="O83" s="16" t="n">
         <v>0</v>
@@ -6690,12 +6690,12 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F84" s="14" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J84" s="14" t="n">
@@ -6741,16 +6741,16 @@
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O84" s="16" t="n">
         <v>0</v>
@@ -6762,12 +6762,12 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30358</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
@@ -6777,12 +6777,12 @@
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARGELES-SUR-MER</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
@@ -6802,29 +6802,29 @@
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30366</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00154569</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" s="12" t="n">
+        <v>255</v>
+      </c>
+      <c r="O85" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P85" s="12" t="n">
@@ -6834,12 +6834,12 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F86" s="14" t="inlineStr">
@@ -6874,29 +6874,29 @@
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="J86" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K86" s="14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-30366</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00154569</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
-        <v>140</v>
-      </c>
-      <c r="O86" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P86" s="15" t="n">
@@ -6906,32 +6906,32 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr">
@@ -6941,32 +6941,32 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="O87" s="16" t="n">
         <v>0</v>
@@ -6978,27 +6978,27 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30044</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>CD29</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>Commande du flux WFS COM pour Inforoute</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F88" s="14" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="G88" s="14" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H88" s="14" t="inlineStr">
@@ -7018,29 +7018,29 @@
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K88" s="14" t="n">
-        <v>0.5</v>
+        <v>7.25</v>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30046</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>00153621</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" s="15" t="n">
+        <v>690</v>
+      </c>
+      <c r="O88" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P88" s="15" t="n">
@@ -7050,12 +7050,12 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30044</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD29</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="G89" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H89" s="11" t="inlineStr">
@@ -7090,23 +7090,23 @@
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>2.42</v>
+        <v>0.5</v>
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-30046</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00153621</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
@@ -7173,18 +7173,18 @@
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N90" s="15" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="O90" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P90" s="15" t="n">
@@ -7245,16 +7245,16 @@
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O91" s="16" t="n">
         <v>0</v>
@@ -7266,32 +7266,32 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G92" s="14" t="inlineStr">
@@ -7301,32 +7301,32 @@
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J92" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N92" s="15" t="n">
-        <v>725</v>
+        <v>787.5</v>
       </c>
       <c r="O92" s="16" t="n">
         <v>0</v>
@@ -7338,30 +7338,32 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E93" s="11" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr">
@@ -7371,34 +7373,34 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" s="12" t="n">
+        <v>725</v>
+      </c>
+      <c r="O93" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P93" s="12" t="n">
@@ -7408,12 +7410,12 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
@@ -7423,13 +7425,11 @@
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E94" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="n">
+        <v/>
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
@@ -7448,23 +7448,23 @@
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K94" s="14" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
@@ -7675,12 +7675,12 @@
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
@@ -7747,18 +7747,18 @@
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N98" s="15" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O98" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P98" s="15" t="n">
@@ -7768,12 +7768,12 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
@@ -7783,11 +7783,13 @@
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E99" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
@@ -7801,34 +7803,34 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>1.25</v>
+        <v>0.6</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" s="12" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O99" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P99" s="12" t="n">
@@ -7838,12 +7840,12 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
@@ -7853,7 +7855,7 @@
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
         </is>
       </c>
       <c r="E100" s="14" t="n">
@@ -7871,28 +7873,28 @@
       </c>
       <c r="H100" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J100" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K100" s="14" t="n">
-        <v>8.25</v>
+        <v>1.25</v>
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N100" s="15" t="n">
@@ -7908,12 +7910,12 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
@@ -7923,7 +7925,7 @@
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -7946,29 +7948,29 @@
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J101" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K101" s="11" t="n">
-        <v>1.5</v>
+        <v>8.25</v>
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O101" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P101" s="12" t="n">
@@ -7978,28 +7980,26 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E102" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E102" s="14" t="n">
+        <v/>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
@@ -8018,29 +8018,29 @@
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J102" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K102" s="14" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N102" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" s="15" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O102" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="15" t="n">
@@ -8050,27 +8050,27 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24216</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>MMM - LITTERALIS Script purge de données</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+          <t>COMMUNE DE SETE</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>Script purge de données</t>
+          <t>Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -8080,27 +8080,35 @@
       </c>
       <c r="G103" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L103" s="11" t="inlineStr"/>
-      <c r="M103" s="11" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L103" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27578</t>
+        </is>
+      </c>
+      <c r="M103" s="11" t="inlineStr">
+        <is>
+          <t>499043</t>
+        </is>
+      </c>
       <c r="N103" s="12" t="n">
         <v>0</v>
       </c>
@@ -8114,26 +8122,28 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24216</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E104" s="14" t="n">
-        <v/>
+          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+        </is>
+      </c>
+      <c r="E104" s="14" t="inlineStr">
+        <is>
+          <t>Script purge de données</t>
+        </is>
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
@@ -8142,35 +8152,27 @@
       </c>
       <c r="G104" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K104" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L104" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27996</t>
-        </is>
-      </c>
-      <c r="M104" s="14" t="inlineStr">
-        <is>
-          <t>501219</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L104" s="14" t="inlineStr"/>
+      <c r="M104" s="14" t="inlineStr"/>
       <c r="N104" s="15" t="n">
         <v>0</v>
       </c>
@@ -8233,12 +8235,12 @@
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
@@ -8254,22 +8256,22 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E106" s="14" t="n">
@@ -8292,23 +8294,23 @@
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K106" s="14" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M106" s="14" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N106" s="15" t="n">
@@ -8324,12 +8326,12 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
@@ -8339,7 +8341,7 @@
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -8362,23 +8364,23 @@
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
@@ -8394,12 +8396,12 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
@@ -8409,7 +8411,7 @@
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E108" s="14" t="n">
@@ -8432,23 +8434,23 @@
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
         <v>13</v>
       </c>
       <c r="K108" s="14" t="n">
-        <v>1.31</v>
+        <v>0.25</v>
       </c>
       <c r="L108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M108" s="14" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N108" s="15" t="n">
@@ -8513,12 +8515,12 @@
       </c>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N109" s="12" t="n">
@@ -8549,7 +8551,7 @@
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E110" s="14" t="n">
@@ -8583,12 +8585,12 @@
       </c>
       <c r="L110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M110" s="14" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N110" s="15" t="n">
@@ -8619,7 +8621,7 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -8653,12 +8655,12 @@
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N111" s="12" t="n">
@@ -8674,22 +8676,22 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E112" s="14" t="n">
@@ -8707,34 +8709,34 @@
       </c>
       <c r="H112" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J112" s="14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K112" s="14" t="n">
-        <v>0.5</v>
+        <v>1.31</v>
       </c>
       <c r="L112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M112" s="14" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N112" s="15" t="n">
-        <v>401</v>
-      </c>
-      <c r="O112" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P112" s="15" t="n">
@@ -8744,22 +8746,22 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21249</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -8775,24 +8777,36 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H113" s="11" t="inlineStr"/>
+      <c r="H113" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K113" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="L113" s="11" t="inlineStr"/>
-      <c r="M113" s="11" t="inlineStr"/>
+      <c r="L113" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27373</t>
+        </is>
+      </c>
+      <c r="M113" s="11" t="inlineStr">
+        <is>
+          <t>466234</t>
+        </is>
+      </c>
       <c r="N113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O113" s="12" t="n">
+        <v>401</v>
+      </c>
+      <c r="O113" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P113" s="12" t="n">
@@ -8802,22 +8816,22 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21249</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="E114" s="14" t="n">
@@ -8833,11 +8847,7 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H114" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H114" s="14" t="inlineStr"/>
       <c r="I114" s="14" t="inlineStr">
         <is>
           <t>23/04/2025</t>
@@ -8847,18 +8857,10 @@
         <v>16</v>
       </c>
       <c r="K114" s="14" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="L114" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28036</t>
-        </is>
-      </c>
-      <c r="M114" s="14" t="inlineStr">
-        <is>
-          <t>483799</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L114" s="14" t="inlineStr"/>
+      <c r="M114" s="14" t="inlineStr"/>
       <c r="N114" s="15" t="n">
         <v>0</v>
       </c>
@@ -8872,22 +8874,22 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -8905,28 +8907,28 @@
       </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J115" s="11" t="n">
         <v>16</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N115" s="12" t="n">
@@ -8942,22 +8944,22 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C116" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E116" s="14" t="n">
@@ -8980,29 +8982,29 @@
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J116" s="14" t="n">
         <v>16</v>
       </c>
       <c r="K116" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M116" s="14" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N116" s="15" t="n">
-        <v>230</v>
-      </c>
-      <c r="O116" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P116" s="15" t="n">
@@ -9012,22 +9014,22 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -9040,27 +9042,39 @@
       </c>
       <c r="G117" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H117" s="11" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H117" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L117" s="11" t="inlineStr"/>
-      <c r="M117" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L117" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M117" s="11" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N117" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O117" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="O117" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P117" s="12" t="n">
@@ -9070,22 +9084,22 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B118" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C118" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D118" s="14" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E118" s="14" t="n">
@@ -9098,35 +9112,23 @@
       </c>
       <c r="G118" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H118" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H118" s="14" t="inlineStr"/>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J118" s="14" t="n">
         <v>17</v>
       </c>
       <c r="K118" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L118" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28027</t>
-        </is>
-      </c>
-      <c r="M118" s="14" t="inlineStr">
-        <is>
-          <t>470688</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L118" s="14" t="inlineStr"/>
+      <c r="M118" s="14" t="inlineStr"/>
       <c r="N118" s="15" t="n">
         <v>0</v>
       </c>
@@ -9140,12 +9142,12 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
@@ -9155,7 +9157,7 @@
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
@@ -9173,28 +9175,28 @@
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I119" s="11" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J119" s="11" t="n">
         <v>17</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="L119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M119" s="11" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N119" s="12" t="n">
@@ -9210,12 +9212,12 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C120" s="14" t="inlineStr">
@@ -9225,7 +9227,7 @@
       </c>
       <c r="D120" s="14" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E120" s="14" t="n">
@@ -9238,27 +9240,35 @@
       </c>
       <c r="G120" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H120" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J120" s="14" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K120" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="L120" s="14" t="inlineStr"/>
-      <c r="M120" s="14" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L120" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27568</t>
+        </is>
+      </c>
+      <c r="M120" s="14" t="inlineStr">
+        <is>
+          <t>471958</t>
+        </is>
+      </c>
       <c r="N120" s="15" t="n">
         <v>0</v>
       </c>
@@ -9272,12 +9282,12 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
@@ -9287,7 +9297,7 @@
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -9310,14 +9320,14 @@
       </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J121" s="11" t="n">
         <v>20</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="L121" s="11" t="inlineStr"/>
       <c r="M121" s="11" t="inlineStr"/>
@@ -9334,22 +9344,22 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C122" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E122" s="14" t="n">
@@ -9357,44 +9367,36 @@
       </c>
       <c r="F122" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G122" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H122" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J122" s="14" t="n">
         <v>20</v>
       </c>
       <c r="K122" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M122" s="14" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L122" s="14" t="inlineStr"/>
+      <c r="M122" s="14" t="inlineStr"/>
       <c r="N122" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="O122" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P122" s="15" t="n">
@@ -9404,22 +9406,22 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -9427,7 +9429,7 @@
       </c>
       <c r="F123" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G123" s="11" t="inlineStr">
@@ -9437,12 +9439,12 @@
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
@@ -9453,16 +9455,16 @@
       </c>
       <c r="L123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M123" s="11" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N123" s="12" t="n">
-        <v>557.145</v>
+        <v>240</v>
       </c>
       <c r="O123" s="16" t="n">
         <v>0</v>
@@ -9474,22 +9476,22 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C124" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E124" s="14" t="n">
@@ -9502,7 +9504,7 @@
       </c>
       <c r="G124" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H124" s="14" t="inlineStr">
@@ -9512,21 +9514,29 @@
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J124" s="14" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K124" s="14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L124" s="14" t="inlineStr"/>
-      <c r="M124" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L124" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M124" s="14" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N124" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O124" s="15" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O124" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P124" s="15" t="n">
@@ -9536,22 +9546,22 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
@@ -9574,25 +9584,17 @@
       </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J125" s="11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K125" s="11" t="n">
         <v>2.5</v>
       </c>
-      <c r="L125" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28003</t>
-        </is>
-      </c>
-      <c r="M125" s="11" t="inlineStr">
-        <is>
-          <t>412981</t>
-        </is>
-      </c>
+      <c r="L125" s="11" t="inlineStr"/>
+      <c r="M125" s="11" t="inlineStr"/>
       <c r="N125" s="12" t="n">
         <v>0</v>
       </c>
@@ -9606,22 +9608,22 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C126" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E126" s="14" t="n">
@@ -9644,17 +9646,25 @@
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J126" s="14" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K126" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L126" s="14" t="inlineStr"/>
-      <c r="M126" s="14" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="L126" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M126" s="14" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
       <c r="N126" s="15" t="n">
         <v>0</v>
       </c>
@@ -9668,22 +9678,22 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -9706,14 +9716,14 @@
       </c>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L127" s="11" t="inlineStr"/>
       <c r="M127" s="11" t="inlineStr"/>
@@ -9730,12 +9740,12 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B128" s="14" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C128" s="14" t="inlineStr">
@@ -9745,7 +9755,7 @@
       </c>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E128" s="14" t="n">
@@ -9758,7 +9768,7 @@
       </c>
       <c r="G128" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H128" s="14" t="inlineStr">
@@ -9768,25 +9778,17 @@
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J128" s="14" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K128" s="14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L128" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M128" s="14" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L128" s="14" t="inlineStr"/>
+      <c r="M128" s="14" t="inlineStr"/>
       <c r="N128" s="15" t="n">
         <v>0</v>
       </c>
@@ -9800,22 +9802,22 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -9828,33 +9830,33 @@
       </c>
       <c r="G129" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J129" s="11" t="n">
         <v>35</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="L129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34532</t>
+          <t>PDMDEP-27990</t>
         </is>
       </c>
       <c r="M129" s="11" t="inlineStr">
         <is>
-          <t>412263</t>
+          <t>406296</t>
         </is>
       </c>
       <c r="N129" s="12" t="n">
@@ -9870,12 +9872,12 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B130" s="14" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C130" s="14" t="inlineStr">
@@ -9885,7 +9887,7 @@
       </c>
       <c r="D130" s="14" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E130" s="14" t="n">
@@ -9908,17 +9910,25 @@
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J130" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K130" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L130" s="14" t="inlineStr"/>
-      <c r="M130" s="14" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L130" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M130" s="14" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N130" s="15" t="n">
         <v>0</v>
       </c>
@@ -9932,28 +9942,26 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E131" s="11" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E131" s="11" t="n">
+        <v/>
       </c>
       <c r="F131" s="11" t="inlineStr">
         <is>
@@ -9967,7 +9975,7 @@
       </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I131" s="11" t="inlineStr">
@@ -9979,7 +9987,7 @@
         <v>35</v>
       </c>
       <c r="K131" s="11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L131" s="11" t="inlineStr"/>
       <c r="M131" s="11" t="inlineStr"/>
@@ -9996,23 +10004,27 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B132" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C132" s="14" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C132" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D132" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E132" s="14" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F132" s="14" t="inlineStr">
@@ -10027,19 +10039,19 @@
       </c>
       <c r="H132" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I132" s="14" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J132" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K132" s="14" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="L132" s="14" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -10056,27 +10068,23 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-2155</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
-        </is>
-      </c>
-      <c r="C133" s="11" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C133" s="11" t="inlineStr"/>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>MONTPELLIER MMM</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr">
         <is>
-          <t>Montée de version + Pastell</t>
+          <t>Déploiement Module AC</t>
         </is>
       </c>
       <c r="F133" s="11" t="inlineStr">
@@ -10091,19 +10099,19 @@
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I133" s="11" t="inlineStr">
         <is>
-          <t>02/08/2023</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J133" s="11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K133" s="11" t="n">
-        <v>0.5</v>
+        <v>6.5</v>
       </c>
       <c r="L133" s="11" t="inlineStr"/>
       <c r="M133" s="11" t="inlineStr"/>
@@ -10120,21 +10128,29 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>PSC-1326</t>
+          <t>PDMDEP-2155</t>
         </is>
       </c>
       <c r="B134" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="C134" s="14" t="inlineStr"/>
+          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+        </is>
+      </c>
+      <c r="C134" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D134" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="E134" s="14" t="inlineStr"/>
+          <t>COMMUNE DE CHAMBERY</t>
+        </is>
+      </c>
+      <c r="E134" s="14" t="inlineStr">
+        <is>
+          <t>Montée de version + Pastell</t>
+        </is>
+      </c>
       <c r="F134" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -10142,17 +10158,21 @@
       </c>
       <c r="G134" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H134" s="14" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H134" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I134" s="14" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>02/08/2023</t>
         </is>
       </c>
       <c r="J134" s="14" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K134" s="14" t="n">
         <v>0.5</v>
@@ -10172,18 +10192,18 @@
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1326</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr"/>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr"/>
@@ -10200,14 +10220,14 @@
       <c r="H135" s="11" t="inlineStr"/>
       <c r="I135" s="11" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J135" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L135" s="11" t="inlineStr"/>
       <c r="M135" s="11" t="inlineStr"/>
@@ -10222,31 +10242,83 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="17" t="inlineStr">
+      <c r="A136" s="13" t="inlineStr">
+        <is>
+          <t>PSC-1320</t>
+        </is>
+      </c>
+      <c r="B136" s="14" t="inlineStr">
+        <is>
+          <t>Commune de ETEL</t>
+        </is>
+      </c>
+      <c r="C136" s="14" t="inlineStr"/>
+      <c r="D136" s="14" t="inlineStr">
+        <is>
+          <t>Commune de ETEL</t>
+        </is>
+      </c>
+      <c r="E136" s="14" t="inlineStr"/>
+      <c r="F136" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G136" s="14" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H136" s="14" t="inlineStr"/>
+      <c r="I136" s="14" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="J136" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K136" s="14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L136" s="14" t="inlineStr"/>
+      <c r="M136" s="14" t="inlineStr"/>
+      <c r="N136" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B136" s="17" t="inlineStr"/>
-      <c r="C136" s="17" t="inlineStr"/>
-      <c r="D136" s="17" t="inlineStr"/>
-      <c r="E136" s="17" t="inlineStr"/>
-      <c r="F136" s="17" t="inlineStr"/>
-      <c r="G136" s="17" t="inlineStr"/>
-      <c r="H136" s="17" t="inlineStr"/>
-      <c r="I136" s="17" t="inlineStr"/>
-      <c r="J136" s="17" t="inlineStr"/>
-      <c r="K136" s="17" t="inlineStr"/>
-      <c r="L136" s="17" t="inlineStr"/>
-      <c r="M136" s="17" t="inlineStr"/>
-      <c r="N136" s="18" t="n">
+      <c r="B137" s="17" t="inlineStr"/>
+      <c r="C137" s="17" t="inlineStr"/>
+      <c r="D137" s="17" t="inlineStr"/>
+      <c r="E137" s="17" t="inlineStr"/>
+      <c r="F137" s="17" t="inlineStr"/>
+      <c r="G137" s="17" t="inlineStr"/>
+      <c r="H137" s="17" t="inlineStr"/>
+      <c r="I137" s="17" t="inlineStr"/>
+      <c r="J137" s="17" t="inlineStr"/>
+      <c r="K137" s="17" t="inlineStr"/>
+      <c r="L137" s="17" t="inlineStr"/>
+      <c r="M137" s="17" t="inlineStr"/>
+      <c r="N137" s="18" t="n">
         <v>67748.694</v>
       </c>
-      <c r="O136" s="18" t="n">
-        <v>8232.900000000001</v>
-      </c>
-      <c r="P136" s="18" t="n">
-        <v>43.33</v>
+      <c r="O137" s="18" t="n">
+        <v>13494.01</v>
+      </c>
+      <c r="P137" s="18" t="n">
+        <v>70.83</v>
       </c>
     </row>
   </sheetData>
@@ -10383,6 +10455,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId129"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId132"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11032,7 +11105,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>139.5</v>
+        <v>140</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>27.25</v>
@@ -11041,10 +11114,10 @@
         <v>7.5</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>174.25</v>
+        <v>174.75</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>62.25</v>
+        <v>64.25</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>601.65</v>
@@ -11074,7 +11147,7 @@
         <v>15.75</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>103.74</v>
@@ -11093,7 +11166,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -11178,16 +11251,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>384320</v>
+        <v>379059</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>144880</v>
+        <v>143761</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>239440</v>
+        <v>235298</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>149136</v>
+        <v>148528</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>21179</v>
@@ -11203,16 +11276,16 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>171713</v>
+        <v>169987</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>66191</v>
+        <v>65072</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>105522</v>
+        <v>104915</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>88107</v>
+        <v>87499</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>11307</v>
@@ -11228,13 +11301,13 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>212607</v>
+        <v>209072</v>
       </c>
       <c r="C7" s="26" t="n">
         <v>78689</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>133918</v>
+        <v>130383</v>
       </c>
       <c r="E7" s="26" t="n">
         <v>61029</v>

--- a/jira_export_2026-08-21.xlsx
+++ b/jira_export_2026-08-21.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>13,494 €</t>
+          <t>14,461 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,7 +760,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>5,360 €</t>
+          <t>6,327 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>358 h</t>
+          <t>364 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -6400,11 +6400,11 @@
       <c r="N79" s="12" t="n">
         <v>700</v>
       </c>
-      <c r="O79" s="16" t="n">
-        <v>0</v>
+      <c r="O79" s="12" t="n">
+        <v>967.05</v>
       </c>
       <c r="P79" s="12" t="n">
-        <v>0</v>
+        <v>78.94</v>
       </c>
     </row>
     <row r="80">
@@ -7025,7 +7025,7 @@
         <v>7</v>
       </c>
       <c r="K88" s="14" t="n">
-        <v>7.25</v>
+        <v>8.75</v>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>9</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>9</v>
       </c>
       <c r="K96" s="14" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>9</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>9</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>9</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>35</v>
       </c>
       <c r="K133" s="11" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="L133" s="11" t="inlineStr"/>
       <c r="M133" s="11" t="inlineStr"/>
@@ -10315,10 +10315,10 @@
         <v>67748.694</v>
       </c>
       <c r="O137" s="18" t="n">
-        <v>13494.01</v>
+        <v>14461.06</v>
       </c>
       <c r="P137" s="18" t="n">
-        <v>70.83</v>
+        <v>74.64</v>
       </c>
     </row>
   </sheetData>
@@ -11105,16 +11105,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>140</v>
+        <v>141.75</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>27.25</v>
+        <v>28.75</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>7.5</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>174.75</v>
+        <v>178</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>64.25</v>
@@ -11124,7 +11124,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>29.6%</t>
         </is>
       </c>
     </row>
@@ -11166,7 +11166,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>96</v>
+        <v>98.5</v>
       </c>
     </row>
   </sheetData>
@@ -11251,10 +11251,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>379059</v>
+        <v>378092</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>143761</v>
+        <v>142794</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>235298</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>169987</v>
+        <v>169020</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>65072</v>
+        <v>64105</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>104915</v>
